--- a/out/car_event_level.xlsx
+++ b/out/car_event_level.xlsx
@@ -2335,6 +2335,9 @@
       <c r="G10">
         <v>0.1339593541450795</v>
       </c>
+      <c r="H10">
+        <v>0.1177987857923867</v>
+      </c>
       <c r="I10">
         <v>0.1265732332089305</v>
       </c>
@@ -2367,6 +2370,9 @@
       </c>
       <c r="S10">
         <v>0.1289965407967708</v>
+      </c>
+      <c r="T10">
+        <v>0.1098562937967604</v>
       </c>
       <c r="U10">
         <v>0.120543764597108</v>
@@ -3408,6 +3414,9 @@
       <c r="G23">
         <v>-0.04723342381874707</v>
       </c>
+      <c r="H23">
+        <v>-0.3416061667035252</v>
+      </c>
       <c r="I23">
         <v>-0.01849838840555718</v>
       </c>
@@ -3440,6 +3449,9 @@
       </c>
       <c r="S23">
         <v>-0.04862322380145653</v>
+      </c>
+      <c r="T23">
+        <v>-0.3740183565905079</v>
       </c>
       <c r="U23">
         <v>-0.02050594228559072</v>
@@ -3485,6 +3497,9 @@
       <c r="G24">
         <v>-0.04723342381874707</v>
       </c>
+      <c r="H24">
+        <v>-0.3416061667035252</v>
+      </c>
       <c r="I24">
         <v>-0.01849838840555718</v>
       </c>
@@ -3517,6 +3532,9 @@
       </c>
       <c r="S24">
         <v>-0.04862322380145653</v>
+      </c>
+      <c r="T24">
+        <v>-0.3740183565905079</v>
       </c>
       <c r="U24">
         <v>-0.02050594228559072</v>
@@ -6218,6 +6236,9 @@
       <c r="G57">
         <v>0.02705988534561676</v>
       </c>
+      <c r="H57">
+        <v>0.0759627162922728</v>
+      </c>
       <c r="I57">
         <v>0.07848588647788246</v>
       </c>
@@ -6250,6 +6271,9 @@
       </c>
       <c r="S57">
         <v>0.0242313723445939</v>
+      </c>
+      <c r="T57">
+        <v>0.06775893045728594</v>
       </c>
       <c r="U57">
         <v>0.0747987919539929</v>
@@ -6295,6 +6319,9 @@
       <c r="G58">
         <v>0.05388915363829971</v>
       </c>
+      <c r="H58">
+        <v>0.09025375405152225</v>
+      </c>
       <c r="I58">
         <v>0.08316476286732255</v>
       </c>
@@ -6327,6 +6354,9 @@
       </c>
       <c r="S58">
         <v>0.05129329438755112</v>
+      </c>
+      <c r="T58">
+        <v>0.08208269125618363</v>
       </c>
       <c r="U58">
         <v>0.07957127410036155</v>
@@ -7285,6 +7315,9 @@
       <c r="G70">
         <v>-0.06064717825152977</v>
       </c>
+      <c r="H70">
+        <v>0.09867108248834389</v>
+      </c>
       <c r="I70">
         <v>-0.07269439470244876</v>
       </c>
@@ -7317,6 +7350,9 @@
       </c>
       <c r="S70">
         <v>-0.06639006303827136</v>
+      </c>
+      <c r="T70">
+        <v>0.08699316984696714</v>
       </c>
       <c r="U70">
         <v>-0.07898250038458468</v>
@@ -7362,6 +7398,9 @@
       <c r="G71">
         <v>0.1808007509557279</v>
       </c>
+      <c r="H71">
+        <v>0.146290184580558</v>
+      </c>
       <c r="I71">
         <v>0.1340831842480544</v>
       </c>
@@ -7394,6 +7433,9 @@
       </c>
       <c r="S71">
         <v>0.1756256311957482</v>
+      </c>
+      <c r="T71">
+        <v>0.1384767092408947</v>
       </c>
       <c r="U71">
         <v>0.1278748644249761</v>
@@ -7522,6 +7564,9 @@
       <c r="G73">
         <v>-0.06064717825152977</v>
       </c>
+      <c r="H73">
+        <v>0.09867108248834389</v>
+      </c>
       <c r="I73">
         <v>-0.07269439470244876</v>
       </c>
@@ -7554,6 +7599,9 @@
       </c>
       <c r="S73">
         <v>-0.06639006303827136</v>
+      </c>
+      <c r="T73">
+        <v>0.08699316984696714</v>
       </c>
       <c r="U73">
         <v>-0.07898250038458468</v>
@@ -7765,6 +7813,9 @@
       <c r="G76">
         <v>-0.06064717825152977</v>
       </c>
+      <c r="H76">
+        <v>0.09867108248834389</v>
+      </c>
       <c r="I76">
         <v>-0.07269439470244876</v>
       </c>
@@ -7797,6 +7848,9 @@
       </c>
       <c r="S76">
         <v>-0.06639006303827136</v>
+      </c>
+      <c r="T76">
+        <v>0.08699316984696714</v>
       </c>
       <c r="U76">
         <v>-0.07898250038458468</v>
@@ -10332,6 +10386,9 @@
       <c r="G107">
         <v>0.01199517706289333</v>
       </c>
+      <c r="H107">
+        <v>0.06177762709218959</v>
+      </c>
       <c r="I107">
         <v>-0.03955788017200901</v>
       </c>
@@ -10364,6 +10421,9 @@
       </c>
       <c r="S107">
         <v>0.009968837205474083</v>
+      </c>
+      <c r="T107">
+        <v>0.05643333275596255</v>
       </c>
       <c r="U107">
         <v>-0.04310231510802486</v>
@@ -10492,6 +10552,9 @@
       <c r="G109">
         <v>0.03716694311618418</v>
       </c>
+      <c r="H109">
+        <v>0.05811007974291782</v>
+      </c>
       <c r="I109">
         <v>0.08513524511258053</v>
       </c>
@@ -10524,6 +10587,9 @@
       </c>
       <c r="S109">
         <v>0.034088650980178</v>
+      </c>
+      <c r="T109">
+        <v>0.052351735553878</v>
       </c>
       <c r="U109">
         <v>0.08049492426412151</v>
@@ -11150,6 +11216,9 @@
       <c r="G117">
         <v>0.01498712768715493</v>
       </c>
+      <c r="H117">
+        <v>0.2200182968697529</v>
+      </c>
       <c r="I117">
         <v>-0.1008724150954476</v>
       </c>
@@ -11182,6 +11251,9 @@
       </c>
       <c r="S117">
         <v>0.01186045091474775</v>
+      </c>
+      <c r="T117">
+        <v>0.2070177619900245</v>
       </c>
       <c r="U117">
         <v>-0.1063643784311717</v>
@@ -11227,6 +11299,9 @@
       <c r="G118">
         <v>0.01498712768715493</v>
       </c>
+      <c r="H118">
+        <v>0.2200182968697529</v>
+      </c>
       <c r="I118">
         <v>-0.1008724150954476</v>
       </c>
@@ -11259,6 +11334,9 @@
       </c>
       <c r="S118">
         <v>0.01186045091474775</v>
+      </c>
+      <c r="T118">
+        <v>0.2070177619900245</v>
       </c>
       <c r="U118">
         <v>-0.1063643784311717</v>
@@ -24999,6 +25077,9 @@
       <c r="G284">
         <v>0.126814359571552</v>
       </c>
+      <c r="H284">
+        <v>0.08215762401440396</v>
+      </c>
       <c r="I284">
         <v>0.1631518696203899</v>
       </c>
@@ -25031,6 +25112,9 @@
       </c>
       <c r="S284">
         <v>0.1246866383337902</v>
+      </c>
+      <c r="T284">
+        <v>0.0762538739143906</v>
       </c>
       <c r="U284">
         <v>0.1591328324539494</v>
@@ -25076,6 +25160,9 @@
       <c r="G285">
         <v>0.126814359571552</v>
       </c>
+      <c r="H285">
+        <v>0.08215762401440396</v>
+      </c>
       <c r="I285">
         <v>0.1631518696203899</v>
       </c>
@@ -25108,6 +25195,9 @@
       </c>
       <c r="S285">
         <v>0.1246866383337902</v>
+      </c>
+      <c r="T285">
+        <v>0.0762538739143906</v>
       </c>
       <c r="U285">
         <v>0.1591328324539494</v>
@@ -25153,6 +25243,9 @@
       <c r="G286">
         <v>0.126814359571552</v>
       </c>
+      <c r="H286">
+        <v>0.08215762401440396</v>
+      </c>
       <c r="I286">
         <v>0.1631518696203899</v>
       </c>
@@ -25185,6 +25278,9 @@
       </c>
       <c r="S286">
         <v>0.1246866383337902</v>
+      </c>
+      <c r="T286">
+        <v>0.0762538739143906</v>
       </c>
       <c r="U286">
         <v>0.1591328324539494</v>
@@ -25894,6 +25990,9 @@
       <c r="G295">
         <v>-0.01462733584555476</v>
       </c>
+      <c r="H295">
+        <v>0.07100159608205447</v>
+      </c>
       <c r="I295">
         <v>0.03180026885406551</v>
       </c>
@@ -25926,6 +26025,9 @@
       </c>
       <c r="S295">
         <v>-0.01661380066265478</v>
+      </c>
+      <c r="T295">
+        <v>0.06301645082850307</v>
       </c>
       <c r="U295">
         <v>0.02876015217526321</v>
@@ -27631,6 +27733,9 @@
       <c r="G316">
         <v>-0.0773799923652112</v>
       </c>
+      <c r="H316">
+        <v>0.1747513981346532</v>
+      </c>
       <c r="I316">
         <v>0.01801882264906618</v>
       </c>
@@ -27663,6 +27768,9 @@
       </c>
       <c r="S316">
         <v>-0.08324542945427976</v>
+      </c>
+      <c r="T316">
+        <v>0.1561399740605403</v>
       </c>
       <c r="U316">
         <v>0.009577634355690161</v>
@@ -29202,6 +29310,9 @@
       <c r="G335">
         <v>-0.01157298427952391</v>
       </c>
+      <c r="H335">
+        <v>-0.0716362060035417</v>
+      </c>
       <c r="I335">
         <v>-0.02273200217808979</v>
       </c>
@@ -29234,6 +29345,9 @@
       </c>
       <c r="S335">
         <v>-0.01234182603038741</v>
+      </c>
+      <c r="T335">
+        <v>-0.07714181925730315</v>
       </c>
       <c r="U335">
         <v>-0.02389522796953972</v>
@@ -30547,6 +30661,9 @@
       <c r="G352">
         <v>-0.009828616181616123</v>
       </c>
+      <c r="H352">
+        <v>0.2167437831460712</v>
+      </c>
       <c r="I352">
         <v>-0.1705343974623146</v>
       </c>
@@ -30579,6 +30696,9 @@
       </c>
       <c r="S352">
         <v>-0.0155775905028906</v>
+      </c>
+      <c r="T352">
+        <v>0.2017309000294648</v>
       </c>
       <c r="U352">
         <v>-0.1789296324811622</v>
@@ -30624,6 +30744,9 @@
       <c r="G353">
         <v>-0.009828616181616123</v>
       </c>
+      <c r="H353">
+        <v>0.2167437831460712</v>
+      </c>
       <c r="I353">
         <v>-0.1705343974623146</v>
       </c>
@@ -30656,6 +30779,9 @@
       </c>
       <c r="S353">
         <v>-0.0155775905028906</v>
+      </c>
+      <c r="T353">
+        <v>0.2017309000294648</v>
       </c>
       <c r="U353">
         <v>-0.1789296324811622</v>
@@ -31199,6 +31325,9 @@
       <c r="G360">
         <v>0.04212969529927524</v>
       </c>
+      <c r="H360">
+        <v>0.05146559185327104</v>
+      </c>
       <c r="I360">
         <v>-0.04474997510549061</v>
       </c>
@@ -31231,6 +31360,9 @@
       </c>
       <c r="S360">
         <v>0.03444163065711241</v>
+      </c>
+      <c r="T360">
+        <v>0.03845388395428734</v>
       </c>
       <c r="U360">
         <v>-0.05485760754311726</v>
@@ -32014,12 +32146,18 @@
       <c r="D370">
         <v>-0.03714345463344626</v>
       </c>
+      <c r="E370">
+        <v>-0.05391811384414258</v>
+      </c>
       <c r="F370">
         <v>0.04034407084406755</v>
       </c>
       <c r="G370">
         <v>-0.04533851138545419</v>
       </c>
+      <c r="H370">
+        <v>-0.08612621836171475</v>
+      </c>
       <c r="I370">
         <v>-0.04914859725895759</v>
       </c>
@@ -32044,11 +32182,17 @@
       <c r="P370">
         <v>-0.03825835463383687</v>
       </c>
+      <c r="Q370">
+        <v>-0.05725655133065169</v>
+      </c>
       <c r="R370">
         <v>0.03973058103158818</v>
       </c>
       <c r="S370">
         <v>-0.0478641207561679</v>
+      </c>
+      <c r="T370">
+        <v>-0.09449615973920178</v>
       </c>
       <c r="U370">
         <v>-0.0526913509458013</v>
@@ -32260,6 +32404,9 @@
       <c r="G373">
         <v>0.02171096941216699</v>
       </c>
+      <c r="H373">
+        <v>-0.01587903564655402</v>
+      </c>
       <c r="I373">
         <v>0.01336447775528016</v>
       </c>
@@ -32292,6 +32439,9 @@
       </c>
       <c r="S373">
         <v>0.01858523830333877</v>
+      </c>
+      <c r="T373">
+        <v>-0.02525966675923796</v>
       </c>
       <c r="U373">
         <v>0.007209250902007137</v>
@@ -32328,12 +32478,18 @@
       <c r="D374">
         <v>-0.04356270676573448</v>
       </c>
+      <c r="E374">
+        <v>-0.02918233166672324</v>
+      </c>
       <c r="F374">
         <v>0.03596534373904592</v>
       </c>
       <c r="G374">
         <v>-0.0199527999771707</v>
       </c>
+      <c r="H374">
+        <v>-0.07880422017739985</v>
+      </c>
       <c r="I374">
         <v>-0.02274402459891334</v>
       </c>
@@ -32358,11 +32514,17 @@
       <c r="P374">
         <v>-0.04477109155691042</v>
       </c>
+      <c r="Q374">
+        <v>-0.03175625115614819</v>
+      </c>
       <c r="R374">
         <v>0.03532214724314303</v>
       </c>
       <c r="S374">
         <v>-0.02251638521261914</v>
+      </c>
+      <c r="T374">
+        <v>-0.08725081192433028</v>
       </c>
       <c r="U374">
         <v>-0.02633956788620633</v>
